--- a/data/agro/updated_agro.xlsx
+++ b/data/agro/updated_agro.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'crop_start_date': datetime.date(2020, 4, 20), 'crop_start_type': 'sowing', 'crop_end_date': datetime.date(2020, 9, 24), 'crop_end_type': 'harvest', 'max_duration': 400, 'crop_name': 'potato', 'variety_name': 'Potato_701'}</t>
+          <t>{'crop_start_date': datetime.date(2020, 4, 21), 'crop_start_type': 'sowing', 'crop_end_date': datetime.date(2020, 9, 24), 'crop_end_type': 'harvest', 'max_duration': 400, 'crop_name': 'potato', 'variety_name': 'Potato_701'}</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>43941</v>
+        <v>43942</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
